--- a/策划/excel/3_Dice.xlsx
+++ b/策划/excel/3_Dice.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\策划\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29280" windowHeight="13485"/>
+    <workbookView windowWidth="30435" windowHeight="15735"/>
   </bookViews>
   <sheets>
     <sheet name="3_Dice" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -79,40 +79,46 @@
     <t>client</t>
   </si>
   <si>
-    <t>巨剑</t>
+    <t>符文</t>
+  </si>
+  <si>
+    <t>[1,2]</t>
+  </si>
+  <si>
+    <t>盾牌</t>
+  </si>
+  <si>
+    <t>[3,4]</t>
+  </si>
+  <si>
+    <t>斧头</t>
+  </si>
+  <si>
+    <t>[5,6]</t>
+  </si>
+  <si>
+    <t>虎鲸</t>
   </si>
   <si>
     <t>[1]</t>
   </si>
   <si>
-    <t>印记</t>
+    <t>海浪</t>
   </si>
   <si>
     <t>[2,3]</t>
   </si>
   <si>
-    <t>坚盾</t>
+    <t>残月</t>
   </si>
   <si>
     <t>[4,5]</t>
   </si>
   <si>
-    <t>爪痕</t>
+    <t>镰刃</t>
   </si>
   <si>
     <t>[6]</t>
-  </si>
-  <si>
-    <t>虎鲸</t>
-  </si>
-  <si>
-    <t>海浪</t>
-  </si>
-  <si>
-    <t>残月</t>
-  </si>
-  <si>
-    <t>镰刃</t>
   </si>
   <si>
     <t>匕首</t>
@@ -137,14 +143,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,154 +599,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1059,7 +1058,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5916666666667" customWidth="1"/>
@@ -1220,7 +1219,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:7">
       <c r="A9" s="1">
-        <v>30004</v>
+        <v>30005</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>21</v>
@@ -1229,7 +1228,7 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>22</v>
@@ -1237,7 +1236,7 @@
     </row>
     <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="1">
-        <v>30005</v>
+        <v>30006</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -1249,55 +1248,55 @@
         <v>10002</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="1">
-        <v>30006</v>
+        <v>30007</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>10002</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="1">
-        <v>30007</v>
+        <v>30008</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>10002</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="1">
-        <v>30008</v>
+        <v>30009</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>22</v>
@@ -1305,89 +1304,72 @@
     </row>
     <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="1">
-        <v>30009</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>30010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
       </c>
       <c r="D14">
         <v>10003</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:7">
       <c r="A15" s="1">
-        <v>30010</v>
+        <v>30011</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>10003</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="1">
-        <v>30011</v>
+        <v>30012</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>10003</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="1">
-        <v>30012</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17">
-        <v>10003</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:1">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:1">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" customHeight="1" spans="1:5">
+    <row r="19" customHeight="1" spans="1:1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="1:5">
+    <row r="20" customHeight="1" spans="1:1">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" customHeight="1" spans="1:5">
+    <row r="21" customHeight="1" spans="1:1">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" customHeight="1" spans="1:1">
       <c r="A22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
